--- a/artfynd/A 35012-2024 artfynd.xlsx
+++ b/artfynd/A 35012-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7120002</v>
+        <v>7128642</v>
       </c>
       <c r="B2" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636123.0736620484</v>
+        <v>636208</v>
       </c>
       <c r="R2" t="n">
-        <v>6556912.917913032</v>
+        <v>6556738</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,24 +747,14 @@
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35266</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35272</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,42 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7120193</v>
+        <v>7118686</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636123.0736620484</v>
+        <v>636091</v>
       </c>
       <c r="R3" t="n">
-        <v>6556912.917913032</v>
+        <v>6557044</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,24 +853,14 @@
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35260</t>
+          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Ingrid Thomasson  ID;35270</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,42 +887,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7120783</v>
+        <v>7125097</v>
       </c>
       <c r="B4" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636123.0736620484</v>
+        <v>636123</v>
       </c>
       <c r="R4" t="n">
-        <v>6556912.917913032</v>
+        <v>6556913</v>
       </c>
       <c r="S4" t="n">
         <v>30</v>
@@ -994,24 +959,14 @@
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35264</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35263</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7119042</v>
+        <v>7120783</v>
       </c>
       <c r="B5" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1082,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636123.0736620484</v>
+        <v>636123</v>
       </c>
       <c r="R5" t="n">
-        <v>6556912.917913032</v>
+        <v>6556913</v>
       </c>
       <c r="S5" t="n">
         <v>30</v>
@@ -1115,24 +1065,14 @@
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Ingrid Thomasson  ID;35265</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35264</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,42 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7125097</v>
+        <v>7119042</v>
       </c>
       <c r="B6" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1203,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636123.0736620484</v>
+        <v>636123</v>
       </c>
       <c r="R6" t="n">
-        <v>6556912.917913032</v>
+        <v>6556913</v>
       </c>
       <c r="S6" t="n">
         <v>30</v>
@@ -1236,24 +1171,14 @@
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35263</t>
+          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Ingrid Thomasson  ID;35265</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,42 +1205,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7128552</v>
+        <v>7120002</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636123.0736620484</v>
+        <v>636123</v>
       </c>
       <c r="R7" t="n">
-        <v>6556912.917913032</v>
+        <v>6556913</v>
       </c>
       <c r="S7" t="n">
         <v>30</v>
@@ -1357,24 +1277,14 @@
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35262</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35266</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7128642</v>
+        <v>7128552</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,26 +1322,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1445,13 +1350,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636208.0409632304</v>
+        <v>636123</v>
       </c>
       <c r="R8" t="n">
-        <v>6556738.205904047</v>
+        <v>6556913</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,24 +1383,14 @@
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-10-19</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35272</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35262</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,6 +1414,112 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7120193</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bommersvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>636123</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6556913</v>
+      </c>
+      <c r="S9" t="n">
+        <v>30</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-10-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-10-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Ingrid Thomasson  ID;35260</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35012-2024 artfynd.xlsx
+++ b/artfynd/A 35012-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7128642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7118686</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7125097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7120783</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7119042</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7120002</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7128552</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,8 +1560,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7120193</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>